--- a/docs/座位图-9.3.xlsx
+++ b/docs/座位图-9.3.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29400" windowHeight="14120" activeTab="1"/>
+    <workbookView windowWidth="29400" windowHeight="12560" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="学生视角" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
     <t>高一9班座位图</t>
   </si>
   <si>
-    <t>2026.9.1</t>
+    <t>2026.09.21</t>
   </si>
   <si>
     <t>讲    台</t>
@@ -261,7 +261,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -269,6 +268,7 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="14"/>
       <color theme="1"/>
       <name val="宋体"/>
@@ -952,7 +952,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -962,19 +962,25 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -989,7 +995,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -998,7 +1004,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1564,355 +1570,356 @@
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" ht="20.4" spans="1:13">
       <c r="A2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="4"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
     </row>
     <row r="3" ht="19.6" customHeight="1" spans="1:13">
-      <c r="A3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="13"/>
+      <c r="A3" s="7"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="15"/>
       <c r="F3" s="2"/>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="H3" s="12"/>
-      <c r="I3" s="12"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="4" t="s">
+      <c r="K3" s="7"/>
+      <c r="L3" s="7"/>
+      <c r="M3" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="4" ht="20.4" spans="1:13">
-      <c r="A4" s="5"/>
-      <c r="C4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
+      <c r="A4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
     </row>
     <row r="5" ht="20.4" spans="1:13">
-      <c r="A5" s="6"/>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="8"/>
+      <c r="B5" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>9</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>8</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="9">
         <v>7</v>
       </c>
-      <c r="F5" s="14" t="s">
+      <c r="F5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>6</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>5</v>
       </c>
-      <c r="I5" s="7">
+      <c r="I5" s="9">
         <v>4</v>
       </c>
-      <c r="J5" s="14" t="s">
+      <c r="J5" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>3</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="9">
         <v>2</v>
       </c>
-      <c r="M5" s="7">
+      <c r="M5" s="9">
         <v>1</v>
       </c>
     </row>
     <row r="6" ht="40" customHeight="1" spans="1:13">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>1</v>
       </c>
-      <c r="B6" s="14"/>
-      <c r="C6" s="9" t="s">
+      <c r="B6" s="16"/>
+      <c r="C6" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F6" s="14"/>
-      <c r="G6" s="15" t="s">
+      <c r="F6" s="16"/>
+      <c r="G6" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="H6" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="9" t="s">
+      <c r="J6" s="16"/>
+      <c r="K6" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="9" t="s">
+      <c r="L6" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="11" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" ht="40" customHeight="1" spans="1:13">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>2</v>
       </c>
-      <c r="B7" s="14"/>
-      <c r="C7" s="9" t="s">
+      <c r="B7" s="16"/>
+      <c r="C7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="F7" s="14"/>
-      <c r="G7" s="9" t="s">
+      <c r="F7" s="16"/>
+      <c r="G7" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="I7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="9" t="s">
+      <c r="J7" s="16"/>
+      <c r="K7" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="9" t="s">
+      <c r="M7" s="11" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="8" ht="40" customHeight="1" spans="1:13">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>3</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="9" t="s">
+      <c r="B8" s="16"/>
+      <c r="C8" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="14"/>
-      <c r="G8" s="9" t="s">
+      <c r="F8" s="16"/>
+      <c r="G8" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="I8" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="9" t="s">
+      <c r="J8" s="16"/>
+      <c r="K8" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="9" t="s">
+      <c r="M8" s="11" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="9" ht="40" customHeight="1" spans="1:13">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="14"/>
-      <c r="C9" s="9" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="E9" s="9" t="s">
+      <c r="E9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="F9" s="14"/>
-      <c r="G9" s="9" t="s">
+      <c r="F9" s="16"/>
+      <c r="G9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="I9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="9" t="s">
+      <c r="J9" s="16"/>
+      <c r="K9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="M9" s="9" t="s">
+      <c r="M9" s="11" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" ht="40" customHeight="1" spans="1:13">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>5</v>
       </c>
-      <c r="B10" s="14"/>
-      <c r="C10" s="9" t="s">
+      <c r="B10" s="16"/>
+      <c r="C10" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="9" t="s">
+      <c r="E10" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="14"/>
-      <c r="G10" s="9" t="s">
+      <c r="F10" s="16"/>
+      <c r="G10" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="17" t="s">
         <v>46</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="17" t="s">
         <v>47</v>
       </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="9" t="s">
+      <c r="J10" s="16"/>
+      <c r="K10" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="M10" s="9" t="s">
+      <c r="M10" s="11" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" ht="40" customHeight="1" spans="1:13">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>6</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="9" t="s">
+      <c r="B11" s="16"/>
+      <c r="C11" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="17" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="14"/>
-      <c r="G11" s="9" t="s">
+      <c r="F11" s="16"/>
+      <c r="G11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="I11" s="9" t="s">
+      <c r="I11" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="J11" s="14"/>
-      <c r="K11" s="9" t="s">
+      <c r="J11" s="16"/>
+      <c r="K11" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="M11" s="9" t="s">
+      <c r="M11" s="11" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="12" ht="40" customHeight="1" spans="1:13">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>7</v>
       </c>
-      <c r="B12" s="14"/>
-      <c r="C12" s="9" t="s">
+      <c r="B12" s="16"/>
+      <c r="C12" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="9" t="s">
+      <c r="E12" s="11" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="14"/>
-      <c r="G12" s="9" t="s">
+      <c r="F12" s="16"/>
+      <c r="G12" s="11" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="J12" s="14"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="15" t="s">
+      <c r="J12" s="16"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="M12" s="16" t="s">
+      <c r="M12" s="18" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" ht="19.6" customHeight="1" spans="1:13">
-      <c r="A13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
-      <c r="L13" s="5"/>
+      <c r="A13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
     </row>
     <row r="14" ht="20.4" spans="1:13">
-      <c r="M14" s="4" t="s">
+      <c r="M14" s="5" t="s">
         <v>68</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A1:M1"/>
+    <mergeCell ref="G2:I2"/>
     <mergeCell ref="G3:I3"/>
     <mergeCell ref="B5:B12"/>
     <mergeCell ref="F5:F12"/>
@@ -1955,341 +1962,343 @@
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
-    </row>
-    <row r="2" spans="1:13">
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" ht="20.4" spans="1:13">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
       <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="G2" s="3"/>
+      <c r="H2" s="4"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
     </row>
     <row r="3" ht="20.4" spans="1:13">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="4"/>
+      <c r="B3" s="5"/>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2"/>
-      <c r="H3" s="3"/>
+      <c r="H3" s="6"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
     </row>
     <row r="4" ht="20.4" spans="1:13">
-      <c r="A4" s="5"/>
+      <c r="A4" s="7"/>
     </row>
     <row r="5" ht="20.4" spans="1:13">
-      <c r="A5" s="6"/>
-      <c r="B5" s="7">
+      <c r="A5" s="8"/>
+      <c r="B5" s="9">
         <v>1</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="9">
         <v>2</v>
       </c>
-      <c r="D5" s="7">
+      <c r="D5" s="9">
         <v>3</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="7">
+      <c r="F5" s="9">
         <v>4</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="9">
         <v>5</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <v>6</v>
       </c>
-      <c r="I5" s="8" t="s">
+      <c r="I5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="9">
         <v>7</v>
       </c>
-      <c r="K5" s="7">
+      <c r="K5" s="9">
         <v>8</v>
       </c>
-      <c r="L5" s="7">
+      <c r="L5" s="9">
         <v>9</v>
       </c>
-      <c r="M5" s="8" t="s">
+      <c r="M5" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="41" customHeight="1" spans="1:13">
-      <c r="A6" s="7">
+      <c r="A6" s="9">
         <v>7</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B6" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="11" t="s">
         <v>66</v>
       </c>
-      <c r="D6" s="9"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="7" t="s">
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="I6" s="10"/>
-      <c r="J6" s="7" t="s">
+      <c r="I6" s="12"/>
+      <c r="J6" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K6" s="7" t="s">
+      <c r="K6" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="M6" s="10"/>
+      <c r="M6" s="12"/>
     </row>
     <row r="7" ht="41" customHeight="1" spans="1:13">
-      <c r="A7" s="7">
+      <c r="A7" s="9">
         <v>6</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="9" t="s">
+      <c r="E7" s="12"/>
+      <c r="F7" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="G7" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="H7" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I7" s="10"/>
-      <c r="J7" s="9" t="s">
+      <c r="I7" s="12"/>
+      <c r="J7" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="K7" s="9" t="s">
+      <c r="K7" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="L7" s="9" t="s">
+      <c r="L7" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="M7" s="10"/>
+      <c r="M7" s="12"/>
     </row>
     <row r="8" ht="41" customHeight="1" spans="1:13">
-      <c r="A8" s="7">
+      <c r="A8" s="9">
         <v>5</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B8" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="C8" s="9" t="s">
+      <c r="C8" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="9" t="s">
+      <c r="E8" s="12"/>
+      <c r="F8" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="G8" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="H8" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="9" t="s">
+      <c r="I8" s="12"/>
+      <c r="J8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="L8" s="9" t="s">
+      <c r="L8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="M8" s="10"/>
+      <c r="M8" s="12"/>
     </row>
     <row r="9" ht="41" customHeight="1" spans="1:13">
-      <c r="A9" s="7">
+      <c r="A9" s="9">
         <v>4</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C9" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="9" t="s">
+      <c r="E9" s="12"/>
+      <c r="F9" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="G9" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="H9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="I9" s="10"/>
-      <c r="J9" s="9" t="s">
+      <c r="I9" s="12"/>
+      <c r="J9" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="L9" s="9" t="s">
+      <c r="L9" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="M9" s="10"/>
+      <c r="M9" s="12"/>
     </row>
     <row r="10" ht="41" customHeight="1" spans="1:13">
-      <c r="A10" s="7">
+      <c r="A10" s="9">
         <v>3</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B10" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="9" t="s">
+      <c r="C10" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="12"/>
+      <c r="F10" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="H10" s="9" t="s">
+      <c r="H10" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="9" t="s">
+      <c r="I10" s="12"/>
+      <c r="J10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="L10" s="9" t="s">
+      <c r="L10" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="12"/>
     </row>
     <row r="11" ht="41" customHeight="1" spans="1:13">
-      <c r="A11" s="7">
+      <c r="A11" s="9">
         <v>2</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D11" s="9" t="s">
+      <c r="D11" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="9" t="s">
+      <c r="E11" s="12"/>
+      <c r="F11" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="G11" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="H11" s="9" t="s">
+      <c r="H11" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="I11" s="10"/>
-      <c r="J11" s="9" t="s">
+      <c r="I11" s="12"/>
+      <c r="J11" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="10"/>
+      <c r="M11" s="12"/>
     </row>
     <row r="12" ht="41" customHeight="1" spans="1:13">
-      <c r="A12" s="7">
+      <c r="A12" s="9">
         <v>1</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="11"/>
-      <c r="F12" s="9" t="s">
+      <c r="E12" s="13"/>
+      <c r="F12" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="H12" s="9" t="s">
+      <c r="H12" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="9" t="s">
+      <c r="I12" s="13"/>
+      <c r="J12" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="11"/>
+      <c r="M12" s="13"/>
     </row>
     <row r="13" ht="20.4" spans="1:13">
-      <c r="A13" s="5"/>
+      <c r="A13" s="7"/>
     </row>
     <row r="14" ht="20.4" spans="1:13">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="F14" s="12" t="s">
+      <c r="B14" s="5"/>
+      <c r="F14" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="G14" s="12"/>
-      <c r="H14" s="12"/>
+      <c r="G14" s="14"/>
+      <c r="H14" s="14"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:L1"/>
+  <mergeCells count="8">
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="F2:H2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
     <mergeCell ref="F14:H14"/>
